--- a/问题1/口径对照_端点与效率与填法.xlsx
+++ b/问题1/口径对照_端点与效率与填法.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>同端点条件下往返口径更省——单向 0.9487 &gt; 0.9，效率更高；差 1325.4530 元（-96.2267%）</t>
+          <t>同端点条件下往返口径更省——单向 0.9487 &gt; 0.9，效率更高；差 1325.4530 元（-3.7733%）</t>
         </is>
       </c>
     </row>
